--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3162,6 +3162,446 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120290513</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Noppen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>381429</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6700514</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120290578</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91861</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Noppen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>381455</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6700525</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120290637</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79642</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Noppen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>381262</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6700309</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120290645</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79511</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Noppen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>381296</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6700270</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120290513</v>
+        <v>120290645</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3176,37 +3176,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3215,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381429</v>
+        <v>381296</v>
       </c>
       <c r="R22" t="n">
-        <v>6700514</v>
+        <v>6700270</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3281,7 +3273,7 @@
         <v>120290578</v>
       </c>
       <c r="B23" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3395,7 +3387,7 @@
         <v>120290637</v>
       </c>
       <c r="B24" t="n">
-        <v>79642</v>
+        <v>79658</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3498,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120290645</v>
+        <v>120290513</v>
       </c>
       <c r="B25" t="n">
-        <v>79511</v>
+        <v>91876</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3510,29 +3502,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381296</v>
+        <v>381429</v>
       </c>
       <c r="R25" t="n">
-        <v>6700270</v>
+        <v>6700514</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120290645</v>
+        <v>120290578</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>91879</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3180,25 +3180,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3207,10 +3215,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381296</v>
+        <v>381455</v>
       </c>
       <c r="R22" t="n">
-        <v>6700270</v>
+        <v>6700525</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3270,10 +3278,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120290578</v>
+        <v>120290645</v>
       </c>
       <c r="B23" t="n">
-        <v>91879</v>
+        <v>79527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3286,33 +3294,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381455</v>
+        <v>381296</v>
       </c>
       <c r="R23" t="n">
-        <v>6700525</v>
+        <v>6700270</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120290578</v>
+        <v>120290645</v>
       </c>
       <c r="B22" t="n">
-        <v>91879</v>
+        <v>79527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3180,33 +3180,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3215,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381455</v>
+        <v>381296</v>
       </c>
       <c r="R22" t="n">
-        <v>6700525</v>
+        <v>6700270</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3278,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120290645</v>
+        <v>120290637</v>
       </c>
       <c r="B23" t="n">
-        <v>79527</v>
+        <v>79658</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3294,21 +3286,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3321,10 +3313,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381296</v>
+        <v>381262</v>
       </c>
       <c r="R23" t="n">
-        <v>6700270</v>
+        <v>6700309</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3384,10 +3376,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120290637</v>
+        <v>120290513</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>91876</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3396,29 +3388,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381262</v>
+        <v>381429</v>
       </c>
       <c r="R24" t="n">
-        <v>6700309</v>
+        <v>6700514</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120290513</v>
+        <v>120290578</v>
       </c>
       <c r="B25" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,30 +3502,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381429</v>
+        <v>381455</v>
       </c>
       <c r="R25" t="n">
-        <v>6700514</v>
+        <v>6700525</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120290645</v>
+        <v>120290578</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>91879</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3180,25 +3180,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3207,10 +3215,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381296</v>
+        <v>381455</v>
       </c>
       <c r="R22" t="n">
-        <v>6700270</v>
+        <v>6700525</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3490,10 +3498,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120290578</v>
+        <v>120290645</v>
       </c>
       <c r="B25" t="n">
-        <v>91879</v>
+        <v>79527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3506,33 +3514,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381455</v>
+        <v>381296</v>
       </c>
       <c r="R25" t="n">
-        <v>6700525</v>
+        <v>6700270</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120290578</v>
+        <v>120290645</v>
       </c>
       <c r="B22" t="n">
-        <v>91879</v>
+        <v>79527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3180,33 +3180,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3215,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381455</v>
+        <v>381296</v>
       </c>
       <c r="R22" t="n">
-        <v>6700525</v>
+        <v>6700270</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3498,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120290645</v>
+        <v>120290578</v>
       </c>
       <c r="B25" t="n">
-        <v>79527</v>
+        <v>91879</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3514,25 +3506,33 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381296</v>
+        <v>381455</v>
       </c>
       <c r="R25" t="n">
-        <v>6700270</v>
+        <v>6700525</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 30301-2024 artfynd.xlsx
+++ b/artfynd/A 30301-2024 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120290645</v>
+        <v>120290637</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>79658</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381296</v>
+        <v>381262</v>
       </c>
       <c r="R22" t="n">
-        <v>6700270</v>
+        <v>6700309</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3270,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120290637</v>
+        <v>120290513</v>
       </c>
       <c r="B23" t="n">
-        <v>79658</v>
+        <v>91876</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3282,29 +3282,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3313,10 +3321,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381262</v>
+        <v>381429</v>
       </c>
       <c r="R23" t="n">
-        <v>6700309</v>
+        <v>6700514</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3376,10 +3384,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120290513</v>
+        <v>120290645</v>
       </c>
       <c r="B24" t="n">
-        <v>91876</v>
+        <v>79527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3388,37 +3396,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4368</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381429</v>
+        <v>381296</v>
       </c>
       <c r="R24" t="n">
-        <v>6700514</v>
+        <v>6700270</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
